--- a/03_Outputs/San_Juan/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/San_Juan/03_Ordenamiento/ordenamiento.xlsx
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.444722473662787</v>
+        <v>0.444722473662786</v>
       </c>
     </row>
     <row r="4">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="E7" s="112">
-        <v>0.282960552706748</v>
+        <v>0.282960552706747</v>
       </c>
     </row>
   </sheetData>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.444722473662787</v>
+        <v>0.444722473662786</v>
       </c>
     </row>
     <row r="3">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.282960552706748</v>
+        <v>0.282960552706747</v>
       </c>
     </row>
   </sheetData>
